--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_ownership.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_ownership.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Defined</t>
+          <t>Gap</t>
         </is>
       </c>
     </row>
@@ -501,12 +501,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Defined</t>
+          <t>Gap</t>
         </is>
       </c>
     </row>
@@ -616,12 +616,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Defined</t>
+          <t>Gap</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
